--- a/Data/Cleaned/Astor Retail Holdings (Pivot).xlsx
+++ b/Data/Cleaned/Astor Retail Holdings (Pivot).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Infotact-Solution-Project-1\Data\Cleaned\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855E9E41-6529-4E54-A74A-2189A1ACE85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D59F59-CE06-464A-8856-BFB44C066EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3A7DEC3A-8B51-42C0-9161-855C12A1F4C1}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="41" r:id="rId2"/>
+    <pivotCache cacheId="46" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -62,12 +62,6 @@
     <t>Categories</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Total Sales by Category</t>
-  </si>
-  <si>
     <t>Jan</t>
   </si>
   <si>
@@ -107,9 +101,6 @@
     <t>Months (2022)</t>
   </si>
   <si>
-    <t>Total Sales by Months</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
@@ -132,9 +123,6 @@
   </si>
   <si>
     <t>Countries</t>
-  </si>
-  <si>
-    <t>Total Sales by Country</t>
   </si>
   <si>
     <t>Dark Green</t>
@@ -188,13 +176,25 @@
     <t>Lowest Selling Item</t>
   </si>
   <si>
-    <t>Eelctronics (USA)</t>
-  </si>
-  <si>
     <t>Clothing (UK)</t>
   </si>
   <si>
     <t>Aster Retail Holdings</t>
+  </si>
+  <si>
+    <t>Total (£)</t>
+  </si>
+  <si>
+    <t>Total Sales (£) by Country</t>
+  </si>
+  <si>
+    <t>Total Sales (£) by Months</t>
+  </si>
+  <si>
+    <t>Total Sales (£) by Category</t>
+  </si>
+  <si>
+    <t>Electronics (USA)</t>
   </si>
 </sst>
 </file>
@@ -217,7 +217,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,6 +242,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -255,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -272,11 +278,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="61">
+  <dxfs count="13">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -304,474 +311,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2041,6 +1580,62 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent1"/>
@@ -4252,16 +3847,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>586740</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>472440</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>1066800</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>163830</xdr:rowOff>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>49530</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4326,7 +3921,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Vaishakh K" refreshedDate="45957.661411342589" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="500" xr:uid="{ECB72067-740D-4706-8D29-EC23937ADA3D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Vaishakh K" refreshedDate="45959.546652777775" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="500" xr:uid="{ECB72067-740D-4706-8D29-EC23937ADA3D}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="14">
     <cacheField name="order_id" numFmtId="0">
@@ -12069,7 +11664,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0719840-6E5B-489D-A63A-FF6035CB2D14}" name="PivotTable10" cacheId="41" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Categories" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0719840-6E5B-489D-A63A-FF6035CB2D14}" name="PivotTable10" cacheId="46" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Categories" fieldListSortAscending="1">
   <location ref="B4:C8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -12770,7 +12365,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Total" fld="11" baseField="0" baseItem="0"/>
+    <dataField name="Total (£)" fld="11" baseField="4" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="1" format="0" series="1">
@@ -12796,7 +12391,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{62F4AED8-D09C-40FD-B56E-663264A4607E}" name="PivotTable12" cacheId="41" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Countries" colHeaderCaption="Categories" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{62F4AED8-D09C-40FD-B56E-663264A4607E}" name="PivotTable12" cacheId="46" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Countries" colHeaderCaption="Categories" fieldListSortAscending="1">
   <location ref="N4:R12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -13160,7 +12755,31 @@
     <dataField name="Total by Country" fld="11" baseField="0" baseItem="0"/>
   </dataFields>
   <conditionalFormats count="4">
-    <conditionalFormat priority="4">
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="3" selected="0">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+            </reference>
+            <reference field="10" count="6">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="2">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
@@ -13208,31 +12827,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="2">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="4" count="3" selected="0">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-            </reference>
-            <reference field="10" count="6">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="1">
+    <conditionalFormat priority="4">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
@@ -13257,7 +12852,7 @@
       </pivotAreas>
     </conditionalFormat>
   </conditionalFormats>
-  <chartFormats count="3">
+  <chartFormats count="4">
     <chartFormat chart="0" format="3" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -13291,6 +12886,18 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="0" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -13305,7 +12912,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9886BB87-E7D5-45D5-9F04-8AAEF76557DC}" name="PivotTable11" cacheId="41" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Months (2022)" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9886BB87-E7D5-45D5-9F04-8AAEF76557DC}" name="PivotTable11" cacheId="46" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Months (2022)" fieldListSortAscending="1">
   <location ref="I4:J17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -14028,10 +13635,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Total" fld="11" baseField="14" baseItem="1"/>
+    <dataField name="Total (£)" fld="11" baseField="13" baseItem="1"/>
   </dataFields>
   <conditionalFormats count="3">
-    <conditionalFormat priority="22">
+    <conditionalFormat priority="20">
       <pivotAreas count="12">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -14279,7 +13886,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="20">
+    <conditionalFormat priority="22">
       <pivotAreas count="12">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -14729,24 +14336,24 @@
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
     <col min="6" max="6" width="16.88671875" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" customWidth="1"/>
     <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25.88671875" customWidth="1"/>
     <col min="12" max="12" width="19.21875" customWidth="1"/>
     <col min="13" max="13" width="14.21875" customWidth="1"/>
     <col min="14" max="14" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.33203125" customWidth="1"/>
-    <col min="16" max="16" width="16.44140625" customWidth="1"/>
-    <col min="17" max="17" width="15.109375" customWidth="1"/>
+    <col min="15" max="15" width="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.109375" customWidth="1"/>
+    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="33.6" x14ac:dyDescent="0.65">
       <c r="G1" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -14755,15 +14362,15 @@
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="C3" s="5"/>
       <c r="I3" s="5" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="J3" s="5"/>
       <c r="N3" s="5" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
@@ -14775,16 +14382,16 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>4</v>
@@ -14798,13 +14405,13 @@
         <v>203010</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J5" s="7">
         <v>54020</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O5" t="s">
         <v>0</v>
@@ -14827,13 +14434,13 @@
         <v>231421</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J6" s="7">
         <v>61316</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O6" s="7">
         <v>28317</v>
@@ -14856,13 +14463,13 @@
         <v>297359</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J7" s="7">
         <v>54013</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O7" s="7">
         <v>43430</v>
@@ -14885,13 +14492,13 @@
         <v>731790</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J8" s="7">
         <v>65379</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O8" s="7">
         <v>33617</v>
@@ -14908,13 +14515,13 @@
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
       <c r="I9" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J9" s="7">
         <v>64927</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="O9" s="7">
         <v>30277</v>
@@ -14931,13 +14538,13 @@
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
       <c r="I10" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J10" s="7">
         <v>64948</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O10" s="7">
         <v>28309</v>
@@ -14954,13 +14561,13 @@
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
       <c r="I11" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J11" s="7">
         <v>61130</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O11" s="7">
         <v>39060</v>
@@ -14977,7 +14584,7 @@
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
       <c r="I12" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J12" s="7">
         <v>96241</v>
@@ -15000,7 +14607,7 @@
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
       <c r="I13" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J13" s="7">
         <v>66313</v>
@@ -15008,7 +14615,7 @@
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
       <c r="I14" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J14" s="7">
         <v>51339</v>
@@ -15016,7 +14623,7 @@
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.3">
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J15" s="7">
         <v>46723</v>
@@ -15024,7 +14631,7 @@
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.3">
       <c r="I16" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J16" s="7">
         <v>45441</v>
@@ -15037,9 +14644,9 @@
       <c r="J17" s="7">
         <v>731790</v>
       </c>
-      <c r="L17" s="3"/>
+      <c r="L17" s="8"/>
       <c r="O17" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="P17" s="3">
         <f>AVERAGE(O6:Q11)</f>
@@ -15054,43 +14661,43 @@
     </row>
     <row r="19" spans="9:17" x14ac:dyDescent="0.3">
       <c r="O19" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="Q19" s="3"/>
     </row>
     <row r="20" spans="9:17" x14ac:dyDescent="0.3">
       <c r="O20" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Q20" s="3"/>
     </row>
     <row r="21" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I21" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q21" s="3"/>
     </row>
     <row r="22" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I22" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -15098,16 +14705,16 @@
     </row>
     <row r="23" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I23" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q23" s="3">
         <v>138661</v>
@@ -15115,10 +14722,10 @@
     </row>
     <row r="24" spans="9:17" x14ac:dyDescent="0.3">
       <c r="O24" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q24" s="3">
         <v>103790</v>
@@ -15126,10 +14733,10 @@
     </row>
     <row r="25" spans="9:17" x14ac:dyDescent="0.3">
       <c r="O25" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q25" s="3">
         <v>60741</v>
@@ -15137,10 +14744,10 @@
     </row>
     <row r="26" spans="9:17" x14ac:dyDescent="0.3">
       <c r="O26" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q26" s="3">
         <v>26520</v>
@@ -15154,65 +14761,65 @@
     <mergeCell ref="G1:K1"/>
   </mergeCells>
   <conditionalFormatting pivot="1" sqref="J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16">
-    <cfRule type="cellIs" dxfId="24" priority="22" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="22" operator="greaterThan">
       <formula>60000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16">
-    <cfRule type="cellIs" dxfId="23" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="21" operator="lessThan">
       <formula>60000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16">
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="20" operator="greaterThan">
       <formula>90000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="cellIs" dxfId="21" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="cellIs" dxfId="20" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="cellIs" dxfId="19" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q26">
-    <cfRule type="cellIs" dxfId="18" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q26">
-    <cfRule type="cellIs" dxfId="17" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q26">
-    <cfRule type="cellIs" dxfId="16" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="O6:Q11">
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="O6:Q11">
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="O6:Q11">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
